--- a/data_preparation/data/argentina/df_etiquetas.xlsx
+++ b/data_preparation/data/argentina/df_etiquetas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D536"/>
+  <dimension ref="A1:D506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -726,8 +726,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>equipo que avanza
-boca juniors</t>
+          <t>estudiantes</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -745,7 +744,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>estudiantes</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -763,7 +762,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -781,7 +780,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>huracan</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -799,7 +798,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>huracan</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -817,7 +816,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>lanus</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -835,7 +834,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>newell s</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -853,7 +852,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lanus</t>
+          <t>nueva chicago</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -871,7 +870,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>newell s</t>
+          <t>olimpo</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -889,7 +888,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nueva chicago</t>
+          <t>patronato</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -907,7 +906,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>olimpo</t>
+          <t>platense</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -925,7 +924,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>patronato</t>
+          <t>quilmes</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -943,7 +942,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>platense</t>
+          <t>racing club</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -961,7 +960,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>quilmes</t>
+          <t>river plate</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -979,7 +978,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>racing club</t>
+          <t>rosario central</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -997,7 +996,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>river plate</t>
+          <t>san lorenzo</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1015,7 +1014,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rosario central</t>
+          <t>sarmiento</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1033,7 +1032,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>san lorenzo</t>
+          <t>talleres</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1051,7 +1050,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>san martin s j</t>
+          <t>temperley</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1069,7 +1068,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>san martin tuc</t>
+          <t>tigre</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1087,7 +1086,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sarmiento</t>
+          <t>union santa fe</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1105,7 +1104,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>talleres</t>
+          <t>velez sarsfield</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1118,16 +1117,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>equipo_loc</t>
+          <t>equipo_vis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>temperley</t>
+          <t>aldosivi</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1136,16 +1135,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>equipo_loc</t>
+          <t>equipo_vis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tigre</t>
+          <t>all boys</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1154,16 +1153,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>equipo_loc</t>
+          <t>equipo_vis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>union santa fe</t>
+          <t>argentinos juniors</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1172,16 +1171,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>equipo_loc</t>
+          <t>equipo_vis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>velez sarsfield</t>
+          <t>arsenal sarandi</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1195,11 +1194,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>aldosivi</t>
+          <t>atletico  rafaela</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1213,11 +1212,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>all boys</t>
+          <t>atletico  tucuman</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -1231,11 +1230,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>argentinos juniors</t>
+          <t>banfield</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -1249,11 +1248,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>arsenal sarandi</t>
+          <t>barracas central</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -1267,11 +1266,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>atletico  rafaela</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -1285,11 +1284,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>atletico  tucuman</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -1303,11 +1302,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>banfield</t>
+          <t>central cordoba</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -1321,11 +1320,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>chacarita</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
@@ -1339,11 +1338,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>colon</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
@@ -1357,11 +1356,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>boca juniors</t>
+          <t>crucero del norte</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -1375,11 +1374,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>central cordoba</t>
+          <t>defensa y justicia</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
@@ -1393,11 +1392,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>chacarita</t>
+          <t>estudiantes</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -1411,11 +1410,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>colon</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
@@ -1429,11 +1428,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>crucero del norte</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
@@ -1447,11 +1446,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>defensa y justicia</t>
+          <t>huracan</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
@@ -1465,11 +1464,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>estudiantes</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
@@ -1483,11 +1482,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>lanus</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -1501,11 +1500,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>newell s</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
@@ -1519,11 +1518,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>huracan</t>
+          <t>nueva chicago</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -1537,11 +1536,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>olimpo</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
@@ -1555,11 +1554,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>patronato</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
@@ -1573,11 +1572,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>lanus</t>
+          <t>platense</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
@@ -1591,11 +1590,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>newell s</t>
+          <t>quilmes</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
@@ -1609,11 +1608,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>nueva chicago</t>
+          <t>racing club</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67">
@@ -1627,11 +1626,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>olimpo</t>
+          <t>river plate</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68">
@@ -1645,11 +1644,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>patronato</t>
+          <t>rosario central</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
@@ -1663,11 +1662,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>platense</t>
+          <t>san lorenzo</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
@@ -1681,11 +1680,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>quilmes</t>
+          <t>sarmiento</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71">
@@ -1699,11 +1698,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>racing club</t>
+          <t>talleres</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72">
@@ -1717,11 +1716,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>river plate</t>
+          <t>temperley</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73">
@@ -1735,11 +1734,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>rosario central</t>
+          <t>tigre</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
@@ -1753,11 +1752,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>san lorenzo</t>
+          <t>union santa fe</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75">
@@ -1771,11 +1770,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>san martin s j</t>
+          <t>velez sarsfield</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76">
@@ -1784,16 +1783,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>equipo_vis</t>
+          <t>arbitro</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>san martin tuc</t>
+          <t xml:space="preserve">abal d   arg </t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1802,16 +1801,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>equipo_vis</t>
+          <t>arbitro</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sarmiento</t>
+          <t xml:space="preserve">acita f   arg </t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -1820,16 +1819,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>equipo_vis</t>
+          <t>arbitro</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>talleres</t>
+          <t xml:space="preserve">alvarez l   arg </t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -1838,16 +1837,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>equipo_vis</t>
+          <t>arbitro</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>temperley</t>
+          <t xml:space="preserve">arasa n   arg </t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -1856,16 +1855,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>equipo_vis</t>
+          <t>arbitro</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>tigre</t>
+          <t xml:space="preserve">arganaraz p   arg </t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -1874,16 +1873,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>equipo_vis</t>
+          <t>arbitro</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>union santa fe</t>
+          <t xml:space="preserve">balino j   arg </t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -1892,16 +1891,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>equipo_vis</t>
+          <t>arbitro</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>velez sarsfield</t>
+          <t xml:space="preserve">barraza j   arg </t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -1915,11 +1914,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">abal d   arg </t>
+          <t xml:space="preserve">beligoy f   arg </t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -1933,11 +1932,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">acita f   arg </t>
+          <t xml:space="preserve">bocca b   arg </t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -1951,11 +1950,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">alvarez l   arg </t>
+          <t xml:space="preserve">broggi j   arg </t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -1969,11 +1968,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">arasa n   arg </t>
+          <t xml:space="preserve">castro a   fra </t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -1987,11 +1986,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">arganaraz p   arg </t>
+          <t xml:space="preserve">ceballos d   arg </t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -2005,11 +2004,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">balino j   arg </t>
+          <t xml:space="preserve">comesana l   arg </t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89">
@@ -2023,11 +2022,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">barraza j   arg </t>
+          <t xml:space="preserve">delfino g   arg </t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
@@ -2041,11 +2040,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">beligoy f   arg </t>
+          <t xml:space="preserve">diaz p   arg </t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91">
@@ -2059,11 +2058,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">bocca b   arg </t>
+          <t xml:space="preserve">dovalo p   arg </t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -2077,11 +2076,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">broggi j   arg </t>
+          <t xml:space="preserve">echavarria p   arg </t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
@@ -2095,11 +2094,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">castro a   fra </t>
+          <t xml:space="preserve">echenique f   arg </t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
@@ -2113,11 +2112,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">ceballos d   arg </t>
+          <t xml:space="preserve">echeverria p   arg </t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
@@ -2131,11 +2130,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">comesana l   arg </t>
+          <t xml:space="preserve">ejarque m   arg </t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
@@ -2149,11 +2148,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">damato a   ita </t>
+          <t xml:space="preserve">espinoza d   arg </t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
@@ -2167,11 +2166,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">delfino g   arg </t>
+          <t xml:space="preserve">espinoza f   arg </t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
@@ -2185,11 +2184,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz p   arg </t>
+          <t xml:space="preserve">espinoza f   chi </t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -2203,11 +2202,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">dovalo p   arg </t>
+          <t xml:space="preserve">franklin a   arg </t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100">
@@ -2221,11 +2220,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">echavarria p   arg </t>
+          <t xml:space="preserve">gariano a   arg </t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101">
@@ -2239,11 +2238,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">echenique f   arg </t>
+          <t xml:space="preserve">gariano c   arg </t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
@@ -2257,11 +2256,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">echeverria p   arg </t>
+          <t xml:space="preserve">giannini m   arg </t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103">
@@ -2275,11 +2274,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">ejarque m   arg </t>
+          <t xml:space="preserve">gimenez p   arg </t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104">
@@ -2293,11 +2292,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">espinoza d   arg </t>
+          <t xml:space="preserve">gonzalez m   arg </t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="105">
@@ -2311,11 +2310,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">espinoza f   arg </t>
+          <t xml:space="preserve">herrera d   arg </t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106">
@@ -2329,11 +2328,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">espinoza f   chi </t>
+          <t xml:space="preserve">herrero   h   arg </t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107">
@@ -2347,11 +2346,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">fedorczuk d   uru </t>
+          <t xml:space="preserve">lamolina f  o   arg </t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108">
@@ -2365,11 +2364,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">franklin a   arg </t>
+          <t xml:space="preserve">lamolina n   arg </t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109">
@@ -2383,11 +2382,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">gariano a   arg </t>
+          <t xml:space="preserve">laverni s   arg </t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110">
@@ -2401,11 +2400,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">gariano c   arg </t>
+          <t xml:space="preserve">llobet f   arg </t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111">
@@ -2419,11 +2418,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">giannini m   arg </t>
+          <t xml:space="preserve">lobo medina l   arg </t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112">
@@ -2437,11 +2436,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">gimenez p   arg </t>
+          <t xml:space="preserve">lopez r   arg </t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="113">
@@ -2455,11 +2454,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">gimenez p   uru </t>
+          <t xml:space="preserve">loustau j  c   arg </t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="114">
@@ -2473,11 +2472,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez m   arg </t>
+          <t xml:space="preserve">loustau p   arg </t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115">
@@ -2491,11 +2490,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">herrera d   arg </t>
+          <t xml:space="preserve">lunati p   arg </t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="116">
@@ -2509,11 +2508,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">herrero   h   arg </t>
+          <t xml:space="preserve">magallan r   ven </t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117">
@@ -2527,11 +2526,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">lamolina f  o   arg </t>
+          <t xml:space="preserve">maglio c   arg </t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="118">
@@ -2545,11 +2544,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">lamolina n   arg </t>
+          <t xml:space="preserve">martinez s   arg </t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="119">
@@ -2563,11 +2562,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">laverni s   arg </t>
+          <t xml:space="preserve">mastrangelo h   arg </t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="120">
@@ -2581,11 +2580,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">llobet f   arg </t>
+          <t xml:space="preserve">merlos a   arg </t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="121">
@@ -2599,11 +2598,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">lobo medina l   arg </t>
+          <t xml:space="preserve">paletta h   arg </t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="122">
@@ -2617,11 +2616,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez r   arg </t>
+          <t xml:space="preserve">penel a   arg </t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="123">
@@ -2635,11 +2634,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">loustau j  c   arg </t>
+          <t xml:space="preserve">perez y   arg </t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="124">
@@ -2653,11 +2652,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">loustau p   arg </t>
+          <t xml:space="preserve">pezzotta s   arg </t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="125">
@@ -2671,11 +2670,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">lunati p   arg </t>
+          <t xml:space="preserve">piris e   arg </t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="126">
@@ -2689,11 +2688,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">magallan r   ven </t>
+          <t xml:space="preserve">pitana n   arg </t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="127">
@@ -2707,11 +2706,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">maglio c   arg </t>
+          <t xml:space="preserve">pompei j   arg </t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="128">
@@ -2725,11 +2724,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">martinez s   arg </t>
+          <t xml:space="preserve">possi y   arg </t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="129">
@@ -2743,11 +2742,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastrangelo h   arg </t>
+          <t xml:space="preserve">quiroz l   ecu </t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="130">
@@ -2761,11 +2760,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">merlos a   arg </t>
+          <t xml:space="preserve">ramirez m   arg </t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="131">
@@ -2779,11 +2778,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">paletta h   arg </t>
+          <t xml:space="preserve">ramirez n   arg </t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132">
@@ -2797,11 +2796,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">penel a   arg </t>
+          <t xml:space="preserve">rapallini f   arg </t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="133">
@@ -2815,11 +2814,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">perez y   arg </t>
+          <t xml:space="preserve">rey hilfer l   arg </t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="134">
@@ -2833,11 +2832,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">pezzotta s   arg </t>
+          <t xml:space="preserve">rivero r   arg </t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="135">
@@ -2851,11 +2850,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">piris e   arg </t>
+          <t xml:space="preserve">sosa n   arg </t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="136">
@@ -2869,11 +2868,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">pitana n   arg </t>
+          <t xml:space="preserve">tello f   arg </t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137">
@@ -2887,11 +2886,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">pompei j   arg </t>
+          <t xml:space="preserve">testa s   arg </t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="138">
@@ -2905,11 +2904,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">possi y   arg </t>
+          <t xml:space="preserve">trucco s   arg </t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="139">
@@ -2923,11 +2922,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">quiroz l   ecu </t>
+          <t xml:space="preserve">vigliano m   arg </t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="140">
@@ -2941,11 +2940,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">ramirez m   arg </t>
+          <t xml:space="preserve">vigliano p   arg </t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="141">
@@ -2959,11 +2958,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">ramirez n   arg </t>
+          <t xml:space="preserve">zerillo c   arg </t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142">
@@ -2977,11 +2976,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapallini f   arg </t>
+          <t xml:space="preserve">zunino s   arg </t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="143">
@@ -2993,13 +2992,9 @@
           <t>arbitro</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rey hilfer l   arg </t>
-        </is>
-      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="144">
@@ -3008,16 +3003,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivero r   arg </t>
+          <t>acosta rodrigo</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -3026,16 +3021,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">sosa n   arg </t>
+          <t>adrover adrian</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -3044,16 +3039,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">tello f   arg </t>
+          <t>aguirre diego</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -3062,16 +3057,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">testa s   arg </t>
+          <t>alegre fabian</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -3080,16 +3075,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">trucco s   arg </t>
+          <t>alfaro gustavo</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
@@ -3098,16 +3093,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">vigliano m   arg </t>
+          <t>almeyda matias</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
@@ -3116,16 +3111,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">vigliano p   arg </t>
+          <t>almiron jorge</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
@@ -3134,16 +3129,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">zerillo c   arg </t>
+          <t>alvarez gustavo</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -3152,16 +3147,16 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>arbitro</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">zunino s   arg </t>
+          <t>anastacio martin</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153">
@@ -3170,12 +3165,16 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>arbitro</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>dt_loc</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>apuzzo nestor</t>
+        </is>
+      </c>
       <c r="D153" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
@@ -3189,11 +3188,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>acosta rodrigo</t>
+          <t>arruabarrena rodolfo</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155">
@@ -3207,11 +3206,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>adrover adrian</t>
+          <t>astrada leonardo</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156">
@@ -3225,11 +3224,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>aguirre diego</t>
+          <t>azconzabal juan manuel</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157">
@@ -3243,11 +3242,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>alegre fabian</t>
+          <t>balbo abel</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="158">
@@ -3261,11 +3260,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>alfaro gustavo</t>
+          <t>barbas juan</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="159">
@@ -3279,11 +3278,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>almeyda matias</t>
+          <t>bassedas christian</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160">
@@ -3297,11 +3296,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>almiron jorge</t>
+          <t>battaglia sebastian</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161">
@@ -3315,11 +3314,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>alvarez gustavo</t>
+          <t>bauza edgardo</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="162">
@@ -3333,11 +3332,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>anastacio martin</t>
+          <t>beccacece sebastian</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="163">
@@ -3351,11 +3350,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>apuzzo nestor</t>
+          <t>benitez leandro</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164">
@@ -3369,11 +3368,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>arruabarrena rodolfo</t>
+          <t>benitez leonardo</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165">
@@ -3387,11 +3386,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>astrada leonardo</t>
+          <t>bernardi lucas</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166">
@@ -3405,11 +3404,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>azconzabal juan manuel</t>
+          <t>beron fernando</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="167">
@@ -3423,11 +3422,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>balbo abel</t>
+          <t>berti alfredo</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168">
@@ -3441,11 +3440,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>barbas juan</t>
+          <t>biaggio claudio</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169">
@@ -3459,11 +3458,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>bassedas christian</t>
+          <t>bianchi carlos</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170">
@@ -3477,11 +3476,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>battaglia sebastian</t>
+          <t>bidoglio hector</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="171">
@@ -3495,11 +3494,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>bauza edgardo</t>
+          <t>borghi claudio</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="172">
@@ -3513,11 +3512,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>beccacece sebastian</t>
+          <t>burgos german</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="173">
@@ -3531,11 +3530,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>benitez leandro</t>
+          <t>burruchaga jorge</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="174">
@@ -3549,11 +3548,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>benitez leonardo</t>
+          <t>caixinha pedro</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175">
@@ -3567,11 +3566,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>bernardi lucas</t>
+          <t>camoranesi mauro</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="176">
@@ -3585,11 +3584,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>beron fernando</t>
+          <t>carboni ezequiel</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177">
@@ -3603,11 +3602,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>berti alfredo</t>
+          <t>caruso ricardo</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="178">
@@ -3621,11 +3620,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>biaggio claudio</t>
+          <t>castro fabian</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="179">
@@ -3639,11 +3638,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>bianchi carlos</t>
+          <t>cocca diego</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="180">
@@ -3657,11 +3656,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>bidoglio hector</t>
+          <t>coleoni gustavo</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="181">
@@ -3675,11 +3674,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>borghi claudio</t>
+          <t>comesana julio</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="182">
@@ -3693,11 +3692,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>bovaglio lucas</t>
+          <t>constantin julio</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183">
@@ -3711,11 +3710,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>burgos german</t>
+          <t>coria adrian</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="184">
@@ -3729,11 +3728,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>burruchaga jorge</t>
+          <t>coudet eduardo</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="185">
@@ -3747,11 +3746,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>caixinha pedro</t>
+          <t>coyette walter</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="186">
@@ -3765,11 +3764,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>camoranesi mauro</t>
+          <t>crespo hernan</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="187">
@@ -3783,11 +3782,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>carboni ezequiel</t>
+          <t>dabove diego</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="188">
@@ -3801,11 +3800,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>caruso ricardo</t>
+          <t>damonte israel</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="189">
@@ -3819,11 +3818,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>castro fabian</t>
+          <t>de felippe omar</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="190">
@@ -3837,11 +3836,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>cocca diego</t>
+          <t>de muner pablo</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="191">
@@ -3855,11 +3854,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>coleoni gustavo</t>
+          <t>de paoli rodolfo</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="192">
@@ -3873,11 +3872,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>comesana julio</t>
+          <t>delfino ivan</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="193">
@@ -3891,11 +3890,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>constantin julio</t>
+          <t>demichelis martin</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="194">
@@ -3909,11 +3908,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>coria adrian</t>
+          <t>desabato leandro</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="195">
@@ -3927,11 +3926,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>coudet eduardo</t>
+          <t>diaz cristian</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="196">
@@ -3945,11 +3944,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>coyette walter</t>
+          <t>diaz ramon</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="197">
@@ -3963,11 +3962,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>crespo hernan</t>
+          <t>diez nicolas</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="198">
@@ -3981,11 +3980,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>dabove diego</t>
+          <t>dominguez eduardo</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="199">
@@ -3999,11 +3998,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>damonte israel</t>
+          <t>echeverria mariano</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="200">
@@ -4017,11 +4016,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>de felippe omar</t>
+          <t>erroz diego</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="201">
@@ -4035,11 +4034,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>de muner pablo</t>
+          <t>esmerado gaston</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="202">
@@ -4053,11 +4052,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>de paoli rodolfo</t>
+          <t>espinola dario</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="203">
@@ -4071,11 +4070,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>delfino ivan</t>
+          <t>falcioni julio</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="204">
@@ -4089,11 +4088,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>demichelis martin</t>
+          <t>fernandez leonardo</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="205">
@@ -4107,11 +4106,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>desabato leandro</t>
+          <t>fernandez manuel</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="206">
@@ -4125,11 +4124,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>diaz cristian</t>
+          <t>ferrari paulo</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="207">
@@ -4143,11 +4142,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>diaz ramon</t>
+          <t>ferrero alexis</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="208">
@@ -4161,11 +4160,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>diez nicolas</t>
+          <t>fleitas juan ramon</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="209">
@@ -4179,11 +4178,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>dominguez eduardo</t>
+          <t>flores diego</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="210">
@@ -4197,11 +4196,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>echeverria mariano</t>
+          <t>flores jose oscar</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="211">
@@ -4215,11 +4214,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>erroz diego</t>
+          <t>forestello ruben dario</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="212">
@@ -4233,11 +4232,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>esmerado gaston</t>
+          <t>franco dario</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="213">
@@ -4251,11 +4250,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>espinola dario</t>
+          <t>fuertes esteban</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="214">
@@ -4269,11 +4268,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>falcioni julio</t>
+          <t>funes martin</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="215">
@@ -4287,11 +4286,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>farre guillermo</t>
+          <t>gago fernando</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="216">
@@ -4305,11 +4304,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>fernandez leonardo</t>
+          <t>gallardo marcelo</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="217">
@@ -4323,11 +4322,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>fernandez manuel</t>
+          <t>gallego americo</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="218">
@@ -4341,11 +4340,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ferrari paulo</t>
+          <t>galloni hugo</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="219">
@@ -4359,11 +4358,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ferrero alexis</t>
+          <t>gamboa fernando</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="220">
@@ -4377,11 +4376,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>fleitas juan ramon</t>
+          <t>gandolfi javier</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="221">
@@ -4395,11 +4394,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>flores diego</t>
+          <t>gareca ricardo</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="222">
@@ -4413,11 +4412,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>flores jose oscar</t>
+          <t>garfagnoli fabian</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="223">
@@ -4431,11 +4430,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>forestello ruben dario</t>
+          <t>giunta blas armando</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="224">
@@ -4449,11 +4448,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>franco dario</t>
+          <t>gomez marcelo</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="225">
@@ -4467,11 +4466,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>fuertes esteban</t>
+          <t>gomez sergio</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="226">
@@ -4485,11 +4484,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>funes martin</t>
+          <t>gonzalez esteban</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="227">
@@ -4503,11 +4502,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>gago fernando</t>
+          <t>gonzalez kily</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="228">
@@ -4521,11 +4520,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>gallardo marcelo</t>
+          <t>gonzalez roberto</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="229">
@@ -4539,11 +4538,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>gallego americo</t>
+          <t>gorosito nestor</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="230">
@@ -4557,11 +4556,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>galloni hugo</t>
+          <t>goux marcelo</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="231">
@@ -4575,11 +4574,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>gamboa fernando</t>
+          <t>graciani gabriel</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="232">
@@ -4593,11 +4592,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>gandolfi javier</t>
+          <t>graf claudio</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="233">
@@ -4611,11 +4610,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>gareca ricardo</t>
+          <t>grelak alfredo</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="234">
@@ -4629,11 +4628,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>garfagnoli fabian</t>
+          <t>grondona humberto</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="235">
@@ -4647,11 +4646,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>giunta blas armando</t>
+          <t>guede pablo</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="236">
@@ -4665,11 +4664,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>gomez marcelo</t>
+          <t>guinazu pablo</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="237">
@@ -4683,11 +4682,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>gomez sergio</t>
+          <t>gustavo tognarelli</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="238">
@@ -4701,11 +4700,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>gonzalez esteban</t>
+          <t>heinze gabriel</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="239">
@@ -4719,11 +4718,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>gonzalez kily</t>
+          <t>herron mariano</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="240">
@@ -4737,11 +4736,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>gonzalez roberto</t>
+          <t>holan ariel</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="241">
@@ -4755,11 +4754,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>gorosito nestor</t>
+          <t>hoyos angel guillermo</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="242">
@@ -4773,11 +4772,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>goux marcelo</t>
+          <t>ibarra hugo</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="243">
@@ -4791,11 +4790,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>graciani gabriel</t>
+          <t>insua ruben</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="244">
@@ -4809,11 +4808,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>graf claudio</t>
+          <t>johansen ricardo</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="245">
@@ -4827,11 +4826,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>grelak alfredo</t>
+          <t>kudelka frank</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="246">
@@ -4845,11 +4844,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>grondona humberto</t>
+          <t>larriera mauricio</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="247">
@@ -4863,11 +4862,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>guede pablo</t>
+          <t>lavallen pablo</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="248">
@@ -4881,11 +4880,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>guinazu pablo</t>
+          <t>ledesma cristian</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="249">
@@ -4899,11 +4898,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>gustavo tognarelli</t>
+          <t>lippi sergio</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="250">
@@ -4917,11 +4916,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>heinze gabriel</t>
+          <t>llop juan</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="251">
@@ -4935,11 +4934,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>herron mariano</t>
+          <t>lunari ricardo</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="252">
@@ -4953,11 +4952,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>holan ariel</t>
+          <t>madelon leonardo</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="253">
@@ -4971,11 +4970,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>hoyos angel guillermo</t>
+          <t>maradona diego armando</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="254">
@@ -4989,11 +4988,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ibarra hugo</t>
+          <t>marcelo saralegui</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="255">
@@ -5007,11 +5006,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>insua ruben</t>
+          <t>marini adrian</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="256">
@@ -5025,11 +5024,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>johansen ricardo</t>
+          <t>marini pablo</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="257">
@@ -5043,11 +5042,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>kudelka frank</t>
+          <t>martinez diego hernan</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="258">
@@ -5061,11 +5060,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>labruna omar</t>
+          <t>martini leandro</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="259">
@@ -5079,11 +5078,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>larriera mauricio</t>
+          <t>matosas gustavo</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="260">
@@ -5097,11 +5096,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>lavallen pablo</t>
+          <t>mayor carlos</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="261">
@@ -5115,11 +5114,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ledesma cristian</t>
+          <t>medina alexandre</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="262">
@@ -5133,11 +5132,11 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>lippi sergio</t>
+          <t>mendez sebastian</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="263">
@@ -5151,11 +5150,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>llop juan</t>
+          <t>merlo reinaldo carlos</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="264">
@@ -5169,11 +5168,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>lopez javier</t>
+          <t>messera mariano</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="265">
@@ -5187,11 +5186,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>lunari ricardo</t>
+          <t>milito gabriel</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="266">
@@ -5205,11 +5204,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>madelon leonardo</t>
+          <t>mohamed antonio</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="267">
@@ -5223,11 +5222,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>maradona diego armando</t>
+          <t>monarriz diego</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="268">
@@ -5241,11 +5240,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>marcelo saralegui</t>
+          <t>montero paolo</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="269">
@@ -5259,11 +5258,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>marini adrian</t>
+          <t>mosset marcelo</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="270">
@@ -5277,11 +5276,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>marini pablo</t>
+          <t>munua gustavo</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="271">
@@ -5295,11 +5294,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>markic diego</t>
+          <t>oldra daniel</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="272">
@@ -5313,11 +5312,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>martinez diego hernan</t>
+          <t>orsi favio</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="273">
@@ -5331,11 +5330,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>martini leandro</t>
+          <t>ortiz dario</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="274">
@@ -5349,11 +5348,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>martos ariel</t>
+          <t>osella diego</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="275">
@@ -5367,11 +5366,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>matosas gustavo</t>
+          <t>palermo martin</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="276">
@@ -5385,11 +5384,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>mayor carlos</t>
+          <t>patalano alejandro</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="277">
@@ -5403,11 +5402,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>medina alexandre</t>
+          <t>pellegrino mauricio</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="278">
@@ -5421,11 +5420,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>mendez sebastian</t>
+          <t>pena sebastian</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="279">
@@ -5439,11 +5438,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>merlo reinaldo carlos</t>
+          <t>perazzo walter</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="280">
@@ -5457,11 +5456,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>messera mariano</t>
+          <t>pizzi juan</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="281">
@@ -5475,11 +5474,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>milito gabriel</t>
+          <t>precone luciano</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="282">
@@ -5493,11 +5492,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>mohamed antonio</t>
+          <t>pumpido juan pablo</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="283">
@@ -5511,11 +5510,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>monarriz diego</t>
+          <t>pusineri lucas</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="284">
@@ -5529,11 +5528,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>montero paolo</t>
+          <t>quattrocchi pablo</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="285">
@@ -5547,11 +5546,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>mosset marcelo</t>
+          <t>quiroz fernando</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="286">
@@ -5565,11 +5564,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>munua gustavo</t>
+          <t>radaelli fabio</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="287">
@@ -5583,11 +5582,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>nania alejandro</t>
+          <t>raggio gustavo daniel</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="288">
@@ -5601,11 +5600,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>oldra daniel</t>
+          <t>rambert sebastian</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="289">
@@ -5619,11 +5618,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>orsi favio</t>
+          <t>rezza ricardo</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="290">
@@ -5637,11 +5636,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ortiz dario</t>
+          <t>rivarola german</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="291">
@@ -5655,11 +5654,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>osella diego</t>
+          <t>rodriguez ricardo jose</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="292">
@@ -5673,11 +5672,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>palermo martin</t>
+          <t>romagnoli leandro atilio</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="293">
@@ -5691,11 +5690,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>patalano alejandro</t>
+          <t>romero sebastian</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="294">
@@ -5709,11 +5708,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>pellegrino mauricio</t>
+          <t>rondina sergio</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="295">
@@ -5727,11 +5726,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>pena sebastian</t>
+          <t>ruiz carlos</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="296">
@@ -5745,11 +5744,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>perazzo walter</t>
+          <t>russo miguel</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="297">
@@ -5763,11 +5762,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>pizzi juan</t>
+          <t>sanguinetti javier</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="298">
@@ -5781,11 +5780,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>precone luciano</t>
+          <t>sanzotti raul</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="299">
@@ -5799,11 +5798,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>pumpido juan pablo</t>
+          <t>sava facundo</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="300">
@@ -5817,11 +5816,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>pusineri lucas</t>
+          <t>schelotto guillermo</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="301">
@@ -5835,11 +5834,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>quattrocchi pablo</t>
+          <t>schurrer gabriel</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="302">
@@ -5853,11 +5852,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>quiroz fernando</t>
+          <t>sciacqua mario</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="303">
@@ -5871,11 +5870,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>radaelli fabio</t>
+          <t>sensini roberto</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="304">
@@ -5889,11 +5888,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>raggio gustavo daniel</t>
+          <t>somoza leandro</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="305">
@@ -5907,11 +5906,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>rambert sebastian</t>
+          <t>soso mariano</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="306">
@@ -5925,11 +5924,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>ramos sergio</t>
+          <t>sponton claudio</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="307">
@@ -5943,11 +5942,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>rezza ricardo</t>
+          <t>stillitano leandro</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="308">
@@ -5961,11 +5960,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>rivarola german</t>
+          <t>taffarel adrian</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="309">
@@ -5979,11 +5978,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>rodriguez ricardo jose</t>
+          <t>tevez carlos</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="310">
@@ -5997,11 +5996,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>romagnoli leandro atilio</t>
+          <t>troglio pedro</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="311">
@@ -6015,11 +6014,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>romero sebastian</t>
+          <t>ubeda claudio</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="312">
@@ -6033,11 +6032,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>rondina sergio</t>
+          <t>vaccari julio</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="313">
@@ -6051,11 +6050,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>ruiz carlos</t>
+          <t>vella cristian</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="314">
@@ -6069,11 +6068,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>russo miguel</t>
+          <t>villar diego</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="315">
@@ -6087,11 +6086,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>sanguinetti javier</t>
+          <t>villar diego nicolas</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="316">
@@ -6105,11 +6104,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>sanzotti raul</t>
+          <t>vivas claudio</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="317">
@@ -6123,11 +6122,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>sava facundo</t>
+          <t>vivas nelson</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="318">
@@ -6141,11 +6140,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>schelotto guillermo</t>
+          <t>vojvoda juan pablo</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="319">
@@ -6159,11 +6158,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>schurrer gabriel</t>
+          <t>zielinski ricardo</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="320">
@@ -6177,11 +6176,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>sciacqua mario</t>
+          <t>zubeldia luis</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="321">
@@ -6190,16 +6189,16 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>sensini roberto</t>
+          <t>acosta rodrigo</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -6208,16 +6207,16 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>somoza leandro</t>
+          <t>adrover adrian</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>168</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -6226,16 +6225,16 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>soso mariano</t>
+          <t>aguirre diego</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
@@ -6244,16 +6243,16 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>sponton claudio</t>
+          <t>alegre fabian</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>170</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -6262,16 +6261,16 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>stillitano leandro</t>
+          <t>alfaro gustavo</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>171</v>
+        <v>4</v>
       </c>
     </row>
     <row r="326">
@@ -6280,16 +6279,16 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>taffarel adrian</t>
+          <t>almeyda matias</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>172</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327">
@@ -6298,16 +6297,16 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>tevez carlos</t>
+          <t>almiron jorge</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>173</v>
+        <v>6</v>
       </c>
     </row>
     <row r="328">
@@ -6316,16 +6315,16 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>troglio pedro</t>
+          <t>alvarez gustavo</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>174</v>
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -6334,16 +6333,16 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ubeda claudio</t>
+          <t>anastacio martin</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330">
@@ -6352,16 +6351,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>vaccari julio</t>
+          <t>apuzzo nestor</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>176</v>
+        <v>9</v>
       </c>
     </row>
     <row r="331">
@@ -6370,16 +6369,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>vella cristian</t>
+          <t>arruabarrena rodolfo</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>177</v>
+        <v>10</v>
       </c>
     </row>
     <row r="332">
@@ -6388,16 +6387,16 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>villar diego</t>
+          <t>astrada leonardo</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>178</v>
+        <v>11</v>
       </c>
     </row>
     <row r="333">
@@ -6406,16 +6405,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>villar diego nicolas</t>
+          <t>azconzabal juan manuel</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>179</v>
+        <v>12</v>
       </c>
     </row>
     <row r="334">
@@ -6424,16 +6423,16 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>vivas claudio</t>
+          <t>balbo abel</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>180</v>
+        <v>13</v>
       </c>
     </row>
     <row r="335">
@@ -6442,16 +6441,16 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>vivas nelson</t>
+          <t>barbas juan</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>181</v>
+        <v>14</v>
       </c>
     </row>
     <row r="336">
@@ -6460,16 +6459,16 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>vojvoda juan pablo</t>
+          <t>bassedas christian</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>182</v>
+        <v>15</v>
       </c>
     </row>
     <row r="337">
@@ -6478,16 +6477,16 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>zielinski ricardo</t>
+          <t>battaglia sebastian</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>183</v>
+        <v>16</v>
       </c>
     </row>
     <row r="338">
@@ -6496,16 +6495,16 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>dt_loc</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>zubeldia luis</t>
+          <t>bauza edgardo</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>184</v>
+        <v>17</v>
       </c>
     </row>
     <row r="339">
@@ -6514,12 +6513,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>dt_loc</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr"/>
+          <t>dt_vis</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>beccacece sebastian</t>
+        </is>
+      </c>
       <c r="D339" t="n">
-        <v>185</v>
+        <v>18</v>
       </c>
     </row>
     <row r="340">
@@ -6533,11 +6536,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>acosta rodrigo</t>
+          <t>benitez leandro</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="341">
@@ -6551,11 +6554,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>adrover adrian</t>
+          <t>benitez leonardo</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="342">
@@ -6569,11 +6572,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>aguirre diego</t>
+          <t>bernardi lucas</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="343">
@@ -6587,11 +6590,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>alegre fabian</t>
+          <t>beron fernando</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="344">
@@ -6605,11 +6608,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>alfaro gustavo</t>
+          <t>berti alfredo</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345">
@@ -6623,11 +6626,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>almeyda matias</t>
+          <t>biaggio claudio</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="346">
@@ -6641,11 +6644,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>almiron jorge</t>
+          <t>bianchi carlos</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="347">
@@ -6659,11 +6662,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>alvarez gustavo</t>
+          <t>bidoglio hector</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="348">
@@ -6677,11 +6680,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>anastacio martin</t>
+          <t>blengio juan</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="349">
@@ -6695,11 +6698,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>apuzzo nestor</t>
+          <t>borghi claudio</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350">
@@ -6713,11 +6716,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>arruabarrena rodolfo</t>
+          <t>bravo marcelo rene</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="351">
@@ -6731,11 +6734,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>astrada leonardo</t>
+          <t>burgos german</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="352">
@@ -6749,11 +6752,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>azconzabal juan manuel</t>
+          <t>burruchaga jorge</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="353">
@@ -6767,11 +6770,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>balbo abel</t>
+          <t>caixinha pedro</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="354">
@@ -6785,11 +6788,11 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>barbas juan</t>
+          <t>camoranesi mauro</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="355">
@@ -6803,11 +6806,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>bassedas christian</t>
+          <t>carboni ezequiel</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="356">
@@ -6821,11 +6824,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>battaglia sebastian</t>
+          <t>caruso ricardo</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="357">
@@ -6839,11 +6842,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>bauza edgardo</t>
+          <t>castro fabian</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="358">
@@ -6857,11 +6860,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>beccacece sebastian</t>
+          <t>cocca diego</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="359">
@@ -6875,11 +6878,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>benitez leandro</t>
+          <t>coleoni gustavo</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="360">
@@ -6893,11 +6896,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>benitez leonardo</t>
+          <t>comesana julio</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="361">
@@ -6911,11 +6914,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>bernardi lucas</t>
+          <t>coria adrian</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="362">
@@ -6929,11 +6932,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>beron fernando</t>
+          <t>coudet eduardo</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="363">
@@ -6947,11 +6950,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>berti alfredo</t>
+          <t>coyette walter</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="364">
@@ -6965,11 +6968,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>biaggio claudio</t>
+          <t>crespo hernan</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="365">
@@ -6983,11 +6986,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>bianchi carlos</t>
+          <t>dabove diego</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="366">
@@ -7001,11 +7004,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>bidoglio hector</t>
+          <t>damonte israel</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="367">
@@ -7019,11 +7022,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>blengio juan</t>
+          <t>de felippe omar</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="368">
@@ -7037,11 +7040,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>borghi claudio</t>
+          <t>de leon martin</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="369">
@@ -7055,11 +7058,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>bovaglio lucas</t>
+          <t>de paoli rodolfo</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="370">
@@ -7073,11 +7076,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>bravo marcelo rene</t>
+          <t>delfino ivan</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="371">
@@ -7091,11 +7094,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>burgos german</t>
+          <t>demichelis martin</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="372">
@@ -7109,11 +7112,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>burruchaga jorge</t>
+          <t>diaz cristian</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="373">
@@ -7127,11 +7130,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>caixinha pedro</t>
+          <t>diaz ramon</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
     </row>
     <row r="374">
@@ -7145,11 +7148,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>camoranesi mauro</t>
+          <t>diez nicolas</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="375">
@@ -7163,11 +7166,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>carboni ezequiel</t>
+          <t>dominguez eduardo</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="376">
@@ -7181,11 +7184,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>caruso ricardo</t>
+          <t>donato hugo</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="377">
@@ -7199,11 +7202,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>castro fabian</t>
+          <t>echeverria mariano</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="378">
@@ -7217,11 +7220,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>cocca diego</t>
+          <t>erroz diego</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="379">
@@ -7235,11 +7238,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>coleoni gustavo</t>
+          <t>esmerado gaston</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="380">
@@ -7253,11 +7256,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>comesana julio</t>
+          <t>espinola dario</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="381">
@@ -7271,11 +7274,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>coria adrian</t>
+          <t>falcioni julio</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="382">
@@ -7289,11 +7292,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>coudet eduardo</t>
+          <t>fernandez favio</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="383">
@@ -7307,11 +7310,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>coyette walter</t>
+          <t>fernandez leonardo</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="384">
@@ -7325,11 +7328,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>crespo hernan</t>
+          <t>fernandez manuel</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="385">
@@ -7343,11 +7346,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>dabove diego</t>
+          <t>ferrari paulo</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="386">
@@ -7361,11 +7364,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>damonte israel</t>
+          <t>ferrero alexis</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="387">
@@ -7379,11 +7382,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>de felippe omar</t>
+          <t>fleitas juan ramon</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
     <row r="388">
@@ -7397,11 +7400,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>de leon martin</t>
+          <t>flores diego</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="389">
@@ -7415,11 +7418,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>de paoli rodolfo</t>
+          <t>flores jose oscar</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="390">
@@ -7433,11 +7436,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>delfino ivan</t>
+          <t>forestello ruben dario</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="391">
@@ -7451,11 +7454,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>demichelis martin</t>
+          <t>franco dario</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="392">
@@ -7469,11 +7472,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>desabato leandro</t>
+          <t>fuertes esteban</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="393">
@@ -7487,11 +7490,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>diaz cristian</t>
+          <t>funes martin</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="394">
@@ -7505,11 +7508,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>diaz ramon</t>
+          <t>gago fernando</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="395">
@@ -7523,11 +7526,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>diez nicolas</t>
+          <t>gallardo marcelo</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
     <row r="396">
@@ -7541,11 +7544,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>dominguez eduardo</t>
+          <t>gallego americo</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="397">
@@ -7559,11 +7562,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>donato hugo</t>
+          <t>galloni hugo</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="398">
@@ -7577,11 +7580,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>echeverria mariano</t>
+          <t>gamboa fernando</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="399">
@@ -7595,11 +7598,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>erroz diego</t>
+          <t>gandolfi javier</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="400">
@@ -7613,11 +7616,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>esmerado gaston</t>
+          <t>gareca ricardo</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="401">
@@ -7631,11 +7634,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>espinola dario</t>
+          <t>garfagnoli fabian</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="402">
@@ -7649,11 +7652,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>falcioni julio</t>
+          <t>giunta blas armando</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="403">
@@ -7667,11 +7670,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>farre guillermo</t>
+          <t>gomez marcelo</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
     </row>
     <row r="404">
@@ -7685,11 +7688,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>fernandez favio</t>
+          <t>gomez sergio</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="405">
@@ -7703,11 +7706,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>fernandez leonardo</t>
+          <t>gonzalez esteban</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="406">
@@ -7721,11 +7724,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>fernandez manuel</t>
+          <t>gonzalez kily</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="407">
@@ -7739,11 +7742,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>ferrari paulo</t>
+          <t>gonzalez roberto</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="408">
@@ -7757,11 +7760,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>ferrero alexis</t>
+          <t>gorosito nestor</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="409">
@@ -7775,11 +7778,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>fleitas juan ramon</t>
+          <t>graf claudio</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="410">
@@ -7793,11 +7796,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>flores diego</t>
+          <t>grelak alfredo</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="411">
@@ -7811,11 +7814,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>flores jose oscar</t>
+          <t>grondona humberto</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="412">
@@ -7829,11 +7832,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>forestello ruben dario</t>
+          <t>guede pablo</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="413">
@@ -7847,11 +7850,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>franco dario</t>
+          <t>guinazu pablo</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="414">
@@ -7865,11 +7868,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>fuertes esteban</t>
+          <t>gustavo tognarelli</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="415">
@@ -7883,11 +7886,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>funes martin</t>
+          <t>heinze gabriel</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="416">
@@ -7901,11 +7904,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>gago fernando</t>
+          <t>herron mariano</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="417">
@@ -7919,11 +7922,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>gallardo marcelo</t>
+          <t>holan ariel</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="418">
@@ -7937,11 +7940,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>gallego americo</t>
+          <t>hoyos angel guillermo</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="419">
@@ -7955,11 +7958,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>galloni hugo</t>
+          <t>ibarra hugo</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
     </row>
     <row r="420">
@@ -7973,11 +7976,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>gamboa fernando</t>
+          <t>insua ruben</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="421">
@@ -7991,11 +7994,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>gandolfi javier</t>
+          <t>johansen ricardo</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="422">
@@ -8009,11 +8012,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>garcia floreal</t>
+          <t>kudelka frank</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="423">
@@ -8027,11 +8030,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>gareca ricardo</t>
+          <t>larriera mauricio</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
     </row>
     <row r="424">
@@ -8045,11 +8048,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>garfagnoli fabian</t>
+          <t>lavallen pablo</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="425">
@@ -8063,11 +8066,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>giunta blas armando</t>
+          <t>ledesma cristian</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
     </row>
     <row r="426">
@@ -8081,11 +8084,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>giuntini alejandro</t>
+          <t>lippi sergio</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="427">
@@ -8099,11 +8102,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>gomez marcelo</t>
+          <t>llop juan</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="428">
@@ -8117,11 +8120,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>gomez sergio</t>
+          <t>lunari ricardo</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
     </row>
     <row r="429">
@@ -8135,11 +8138,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>gonzalez esteban</t>
+          <t>madelon leonardo</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="430">
@@ -8153,11 +8156,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>gonzalez kily</t>
+          <t>maradona diego armando</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
     </row>
     <row r="431">
@@ -8171,11 +8174,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>gonzalez roberto</t>
+          <t>marcelo saralegui</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="432">
@@ -8189,11 +8192,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>gorosito nestor</t>
+          <t>marini adrian</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="433">
@@ -8207,11 +8210,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>graciani gabriel</t>
+          <t>marini pablo</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="434">
@@ -8225,11 +8228,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>graf claudio</t>
+          <t>markic diego</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="435">
@@ -8243,11 +8246,11 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>grelak alfredo</t>
+          <t>martinez diego hernan</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="436">
@@ -8261,11 +8264,11 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>grondona humberto</t>
+          <t>martini leandro</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
     </row>
     <row r="437">
@@ -8279,11 +8282,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>guede pablo</t>
+          <t>matosas gustavo</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="438">
@@ -8297,11 +8300,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>guinazu pablo</t>
+          <t>mayor carlos</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="439">
@@ -8315,11 +8318,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>gustavo tognarelli</t>
+          <t>medina alexandre</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>99</v>
+        <v>118</v>
       </c>
     </row>
     <row r="440">
@@ -8333,11 +8336,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>heinze gabriel</t>
+          <t>mendez sebastian</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
     </row>
     <row r="441">
@@ -8351,11 +8354,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>herron mariano</t>
+          <t>merlo reinaldo carlos</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="442">
@@ -8369,11 +8372,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>holan ariel</t>
+          <t>messera mariano</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="443">
@@ -8387,11 +8390,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>hoyos angel guillermo</t>
+          <t>milito gabriel</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
     <row r="444">
@@ -8405,11 +8408,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>ibarra hugo</t>
+          <t>mohamed antonio</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
     </row>
     <row r="445">
@@ -8423,11 +8426,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>insua ruben</t>
+          <t>monarriz diego</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="446">
@@ -8441,11 +8444,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>johansen ricardo</t>
+          <t>montero paolo</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
     </row>
     <row r="447">
@@ -8459,11 +8462,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>kudelka frank</t>
+          <t>mosset marcelo</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>107</v>
+        <v>126</v>
       </c>
     </row>
     <row r="448">
@@ -8477,11 +8480,11 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>labruna omar</t>
+          <t>munua gustavo</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
     </row>
     <row r="449">
@@ -8495,11 +8498,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>larriera mauricio</t>
+          <t>oldra daniel</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="450">
@@ -8513,11 +8516,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>lavallen pablo</t>
+          <t>orsi favio</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="451">
@@ -8531,11 +8534,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>ledesma cristian</t>
+          <t>ortiz dario</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
     </row>
     <row r="452">
@@ -8549,11 +8552,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>lippi sergio</t>
+          <t>osella diego</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
     </row>
     <row r="453">
@@ -8567,11 +8570,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>llop juan</t>
+          <t>palermo martin</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
     </row>
     <row r="454">
@@ -8585,11 +8588,11 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>lopez javier</t>
+          <t>patalano alejandro</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="455">
@@ -8603,11 +8606,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>lunari ricardo</t>
+          <t>pellegrino mauricio</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="456">
@@ -8621,11 +8624,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>madelon leonardo</t>
+          <t>pena sebastian</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
     </row>
     <row r="457">
@@ -8639,11 +8642,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>maradona diego armando</t>
+          <t>perazzo walter</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="458">
@@ -8657,11 +8660,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>marcelo saralegui</t>
+          <t>picerni carlos</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="459">
@@ -8675,11 +8678,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>marini adrian</t>
+          <t>pizzi juan</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
     </row>
     <row r="460">
@@ -8693,11 +8696,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>marini pablo</t>
+          <t>precone luciano</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="461">
@@ -8711,11 +8714,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>markic diego</t>
+          <t>pumpido juan pablo</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="462">
@@ -8729,11 +8732,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>martinez diego hernan</t>
+          <t>pusineri lucas</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>122</v>
+        <v>141</v>
       </c>
     </row>
     <row r="463">
@@ -8747,11 +8750,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>martini leandro</t>
+          <t>quattrocchi pablo</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="464">
@@ -8765,11 +8768,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>matosas gustavo</t>
+          <t>quiroz fernando</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="465">
@@ -8783,11 +8786,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>mayor carlos</t>
+          <t>radaelli fabio</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="466">
@@ -8801,11 +8804,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>medina alexandre</t>
+          <t>raggio gustavo daniel</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
     </row>
     <row r="467">
@@ -8819,11 +8822,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>mendez sebastian</t>
+          <t>rambert sebastian</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="468">
@@ -8837,11 +8840,11 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>merlo reinaldo carlos</t>
+          <t>rezza ricardo</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="469">
@@ -8855,11 +8858,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>messera mariano</t>
+          <t>rivarola german</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>129</v>
+        <v>148</v>
       </c>
     </row>
     <row r="470">
@@ -8873,11 +8876,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>milito gabriel</t>
+          <t>rodriguez ricardo jose</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>130</v>
+        <v>149</v>
       </c>
     </row>
     <row r="471">
@@ -8891,11 +8894,11 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>mohamed antonio</t>
+          <t>romagnoli leandro atilio</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>131</v>
+        <v>150</v>
       </c>
     </row>
     <row r="472">
@@ -8909,11 +8912,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>monarriz diego</t>
+          <t>romero sebastian</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="473">
@@ -8927,11 +8930,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>montero paolo</t>
+          <t>rondina sergio</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="474">
@@ -8945,11 +8948,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>mosset marcelo</t>
+          <t>ruiz carlos</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="475">
@@ -8963,11 +8966,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>munua gustavo</t>
+          <t>russo miguel</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="476">
@@ -8981,11 +8984,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>nania alejandro</t>
+          <t>sanguinetti guillermo</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
     </row>
     <row r="477">
@@ -8999,11 +9002,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>oldra daniel</t>
+          <t>sanguinetti javier</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="478">
@@ -9017,11 +9020,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>orsi favio</t>
+          <t>sanzotti raul</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>138</v>
+        <v>157</v>
       </c>
     </row>
     <row r="479">
@@ -9035,11 +9038,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>ortiz dario</t>
+          <t>sava facundo</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="480">
@@ -9053,11 +9056,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>osella diego</t>
+          <t>schelotto guillermo</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
     </row>
     <row r="481">
@@ -9071,11 +9074,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>palermo martin</t>
+          <t>schurrer gabriel</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
     </row>
     <row r="482">
@@ -9089,11 +9092,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>patalano alejandro</t>
+          <t>sciacqua mario</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="483">
@@ -9107,11 +9110,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>pellegrino mauricio</t>
+          <t>scolari sebastian</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
     </row>
     <row r="484">
@@ -9125,11 +9128,11 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>pena sebastian</t>
+          <t>sensini roberto</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="485">
@@ -9143,11 +9146,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>perazzo walter</t>
+          <t>serrizuela juan jose</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
     </row>
     <row r="486">
@@ -9161,11 +9164,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>picerni carlos</t>
+          <t>somoza leandro</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="487">
@@ -9179,11 +9182,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>pizzi juan</t>
+          <t>soso mariano</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>147</v>
+        <v>166</v>
       </c>
     </row>
     <row r="488">
@@ -9197,11 +9200,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>precone luciano</t>
+          <t>sponton claudio</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="489">
@@ -9215,11 +9218,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>pumpido juan pablo</t>
+          <t>stillitano leandro</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="490">
@@ -9233,11 +9236,11 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>pusineri lucas</t>
+          <t>taffarel adrian</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="491">
@@ -9251,11 +9254,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>quattrocchi pablo</t>
+          <t>tevez carlos</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>151</v>
+        <v>170</v>
       </c>
     </row>
     <row r="492">
@@ -9269,11 +9272,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>quiroz fernando</t>
+          <t>tocalli hugo</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
     </row>
     <row r="493">
@@ -9287,11 +9290,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>radaelli fabio</t>
+          <t>troglio pedro</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
     </row>
     <row r="494">
@@ -9305,11 +9308,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>raggio gustavo daniel</t>
+          <t>ubeda claudio</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>154</v>
+        <v>173</v>
       </c>
     </row>
     <row r="495">
@@ -9323,11 +9326,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>rambert sebastian</t>
+          <t>vaccari julio</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
     </row>
     <row r="496">
@@ -9341,11 +9344,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>ramos sergio</t>
+          <t>vella cristian</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>156</v>
+        <v>175</v>
       </c>
     </row>
     <row r="497">
@@ -9359,11 +9362,11 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>rezza ricardo</t>
+          <t>villar diego</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="498">
@@ -9377,11 +9380,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>rivarola german</t>
+          <t>villar diego nicolas</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="499">
@@ -9395,11 +9398,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>rodriguez ricardo jose</t>
+          <t>vivas claudio</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="500">
@@ -9413,11 +9416,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>romagnoli leandro atilio</t>
+          <t>vivas nelson</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="501">
@@ -9431,11 +9434,11 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>romero sebastian</t>
+          <t>vojvoda juan pablo</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
     </row>
     <row r="502">
@@ -9449,11 +9452,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>rondina sergio</t>
+          <t>zielinski ricardo</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="503">
@@ -9467,11 +9470,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>ruiz carlos</t>
+          <t>zubeldia luis</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="504">
@@ -9480,16 +9483,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>dt_vis</t>
+          <t>equipo_ganador</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>russo miguel</t>
+          <t>Empate</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="505">
@@ -9498,16 +9501,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>dt_vis</t>
+          <t>equipo_ganador</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>sanguinetti guillermo</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -9516,551 +9519,15 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>dt_vis</t>
+          <t>equipo_ganador</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>sanguinetti javier</t>
+          <t>Visitante</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" s="1" t="n">
-        <v>505</v>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>sanzotti raul</t>
-        </is>
-      </c>
-      <c r="D507" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" s="1" t="n">
-        <v>506</v>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>sava facundo</t>
-        </is>
-      </c>
-      <c r="D508" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" s="1" t="n">
-        <v>507</v>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>schelotto guillermo</t>
-        </is>
-      </c>
-      <c r="D509" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" s="1" t="n">
-        <v>508</v>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>schurrer gabriel</t>
-        </is>
-      </c>
-      <c r="D510" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" s="1" t="n">
-        <v>509</v>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>sciacqua mario</t>
-        </is>
-      </c>
-      <c r="D511" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" s="1" t="n">
-        <v>510</v>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>scolari sebastian</t>
-        </is>
-      </c>
-      <c r="D512" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" s="1" t="n">
-        <v>511</v>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>sensini roberto</t>
-        </is>
-      </c>
-      <c r="D513" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" s="1" t="n">
-        <v>512</v>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>serrizuela juan jose</t>
-        </is>
-      </c>
-      <c r="D514" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" s="1" t="n">
-        <v>513</v>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>somoza leandro</t>
-        </is>
-      </c>
-      <c r="D515" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" s="1" t="n">
-        <v>514</v>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>soso mariano</t>
-        </is>
-      </c>
-      <c r="D516" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" s="1" t="n">
-        <v>515</v>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>sponton claudio</t>
-        </is>
-      </c>
-      <c r="D517" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" s="1" t="n">
-        <v>516</v>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>stillitano leandro</t>
-        </is>
-      </c>
-      <c r="D518" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" s="1" t="n">
-        <v>517</v>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>taffarel adrian</t>
-        </is>
-      </c>
-      <c r="D519" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" s="1" t="n">
-        <v>518</v>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>tevez carlos</t>
-        </is>
-      </c>
-      <c r="D520" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" s="1" t="n">
-        <v>519</v>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>tocalli hugo</t>
-        </is>
-      </c>
-      <c r="D521" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" s="1" t="n">
-        <v>520</v>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>troglio pedro</t>
-        </is>
-      </c>
-      <c r="D522" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" s="1" t="n">
-        <v>521</v>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>ubeda claudio</t>
-        </is>
-      </c>
-      <c r="D523" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" s="1" t="n">
-        <v>522</v>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>vaccari julio</t>
-        </is>
-      </c>
-      <c r="D524" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" s="1" t="n">
-        <v>523</v>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>vella cristian</t>
-        </is>
-      </c>
-      <c r="D525" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" s="1" t="n">
-        <v>524</v>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>villar diego</t>
-        </is>
-      </c>
-      <c r="D526" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" s="1" t="n">
-        <v>525</v>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>villar diego nicolas</t>
-        </is>
-      </c>
-      <c r="D527" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" s="1" t="n">
-        <v>526</v>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>vivas claudio</t>
-        </is>
-      </c>
-      <c r="D528" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" s="1" t="n">
-        <v>527</v>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>vivas nelson</t>
-        </is>
-      </c>
-      <c r="D529" t="n">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" s="1" t="n">
-        <v>528</v>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>vojvoda juan pablo</t>
-        </is>
-      </c>
-      <c r="D530" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" s="1" t="n">
-        <v>529</v>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>zielinski ricardo</t>
-        </is>
-      </c>
-      <c r="D531" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" s="1" t="n">
-        <v>530</v>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>zubeldia luis</t>
-        </is>
-      </c>
-      <c r="D532" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" s="1" t="n">
-        <v>531</v>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>dt_vis</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr"/>
-      <c r="D533" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" s="1" t="n">
-        <v>532</v>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>equipo_ganador</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>Empate</t>
-        </is>
-      </c>
-      <c r="D534" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" s="1" t="n">
-        <v>533</v>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>equipo_ganador</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="D535" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" s="1" t="n">
-        <v>534</v>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>equipo_ganador</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>Visitante</t>
-        </is>
-      </c>
-      <c r="D536" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data_preparation/data/argentina/df_etiquetas.xlsx
+++ b/data_preparation/data/argentina/df_etiquetas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D506"/>
+  <dimension ref="A1:D508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">balino j   arg </t>
+          <t xml:space="preserve">arrieta u   col </t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">barraza j   arg </t>
+          <t xml:space="preserve">balino j   arg </t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">beligoy f   arg </t>
+          <t xml:space="preserve">barraza j   arg </t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">bocca b   arg </t>
+          <t xml:space="preserve">beligoy f   arg </t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">broggi j   arg </t>
+          <t xml:space="preserve">bocca b   arg </t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">castro a   fra </t>
+          <t xml:space="preserve">broggi j   arg </t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">ceballos d   arg </t>
+          <t xml:space="preserve">castro a   fra </t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">comesana l   arg </t>
+          <t xml:space="preserve">ceballos d   arg </t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">delfino g   arg </t>
+          <t xml:space="preserve">comesana l   arg </t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz p   arg </t>
+          <t xml:space="preserve">delfino g   arg </t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">dovalo p   arg </t>
+          <t xml:space="preserve">diaz p   arg </t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">echavarria p   arg </t>
+          <t xml:space="preserve">dovalo p   arg </t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">echenique f   arg </t>
+          <t xml:space="preserve">echavarria p   arg </t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">echeverria p   arg </t>
+          <t xml:space="preserve">echenique f   arg </t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ejarque m   arg </t>
+          <t xml:space="preserve">echeverria p   arg </t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">espinoza d   arg </t>
+          <t xml:space="preserve">ejarque m   arg </t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">espinoza f   arg </t>
+          <t xml:space="preserve">espinoza d   arg </t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">espinoza f   chi </t>
+          <t xml:space="preserve">espinoza f   arg </t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">franklin a   arg </t>
+          <t xml:space="preserve">espinoza f   chi </t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">gariano a   arg </t>
+          <t xml:space="preserve">franklin a   arg </t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">gariano c   arg </t>
+          <t xml:space="preserve">gariano a   arg </t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">giannini m   arg </t>
+          <t xml:space="preserve">gariano c   arg </t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">gimenez p   arg </t>
+          <t xml:space="preserve">giannini m   arg </t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez m   arg </t>
+          <t xml:space="preserve">gimenez p   arg </t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">herrera d   arg </t>
+          <t xml:space="preserve">gonzalez m   arg </t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">herrero   h   arg </t>
+          <t xml:space="preserve">herrera d   arg </t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">lamolina f  o   arg </t>
+          <t xml:space="preserve">herrero   h   arg </t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">lamolina n   arg </t>
+          <t xml:space="preserve">lamolina f  o   arg </t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">laverni s   arg </t>
+          <t xml:space="preserve">lamolina n   arg </t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">llobet f   arg </t>
+          <t xml:space="preserve">laverni s   arg </t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">lobo medina l   arg </t>
+          <t xml:space="preserve">llobet f   arg </t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez r   arg </t>
+          <t xml:space="preserve">lobo medina l   arg </t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">loustau j  c   arg </t>
+          <t xml:space="preserve">lopez r   arg </t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">loustau p   arg </t>
+          <t xml:space="preserve">loustau j  c   arg </t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">lunati p   arg </t>
+          <t xml:space="preserve">loustau p   arg </t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">magallan r   ven </t>
+          <t xml:space="preserve">lunati p   arg </t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">maglio c   arg </t>
+          <t xml:space="preserve">magallan r   ven </t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">martinez s   arg </t>
+          <t xml:space="preserve">maglio c   arg </t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastrangelo h   arg </t>
+          <t xml:space="preserve">martinez s   arg </t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">merlos a   arg </t>
+          <t xml:space="preserve">mastrangelo h   arg </t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">paletta h   arg </t>
+          <t xml:space="preserve">merlos a   arg </t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">penel a   arg </t>
+          <t xml:space="preserve">paletta h   arg </t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">perez y   arg </t>
+          <t xml:space="preserve">penel a   arg </t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">pezzotta s   arg </t>
+          <t xml:space="preserve">perez y   arg </t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">piris e   arg </t>
+          <t xml:space="preserve">pezzotta s   arg </t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">pitana n   arg </t>
+          <t xml:space="preserve">piris e   arg </t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">pompei j   arg </t>
+          <t xml:space="preserve">pitana n   arg </t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">possi y   arg </t>
+          <t xml:space="preserve">pompei j   arg </t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">quiroz l   ecu </t>
+          <t xml:space="preserve">possi y   arg </t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">ramirez m   arg </t>
+          <t xml:space="preserve">quiroz l   ecu </t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">ramirez n   arg </t>
+          <t xml:space="preserve">ramirez m   arg </t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapallini f   arg </t>
+          <t xml:space="preserve">ramirez n   arg </t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">rey hilfer l   arg </t>
+          <t xml:space="preserve">rapallini f   arg </t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivero r   arg </t>
+          <t xml:space="preserve">rey hilfer l   arg </t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">sosa n   arg </t>
+          <t xml:space="preserve">rivero r   arg </t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">tello f   arg </t>
+          <t xml:space="preserve">sosa n   arg </t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">testa s   arg </t>
+          <t xml:space="preserve">tello f   arg </t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">trucco s   arg </t>
+          <t xml:space="preserve">testa s   arg </t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">vigliano m   arg </t>
+          <t xml:space="preserve">trucco s   arg </t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">vigliano p   arg </t>
+          <t xml:space="preserve">vigliano m   arg </t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">zerillo c   arg </t>
+          <t xml:space="preserve">vigliano p   arg </t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">zunino s   arg </t>
+          <t xml:space="preserve">zerillo c   arg </t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -2992,7 +2992,11 @@
           <t>arbitro</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zunino s   arg </t>
+        </is>
+      </c>
       <c r="D143" t="n">
         <v>67</v>
       </c>
@@ -3003,16 +3007,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>dt_loc</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>acosta rodrigo</t>
-        </is>
-      </c>
+          <t>arbitro</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="145">
@@ -3026,11 +3026,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>adrover adrian</t>
+          <t>acosta rodrigo</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -3044,11 +3044,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>aguirre diego</t>
+          <t>adrover adrian</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -3062,11 +3062,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>alegre fabian</t>
+          <t>aguirre diego</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>alfaro gustavo</t>
+          <t>alegre fabian</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -3098,11 +3098,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>almeyda matias</t>
+          <t>alfaro gustavo</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
@@ -3116,11 +3116,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>almiron jorge</t>
+          <t>almeyda matias</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -3134,11 +3134,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>alvarez gustavo</t>
+          <t>almiron jorge</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
@@ -3152,11 +3152,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>anastacio martin</t>
+          <t>alvarez gustavo</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -3170,11 +3170,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>apuzzo nestor</t>
+          <t>anastacio martin</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -3188,11 +3188,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>arruabarrena rodolfo</t>
+          <t>apuzzo nestor</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155">
@@ -3206,11 +3206,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>astrada leonardo</t>
+          <t>arruabarrena rodolfo</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156">
@@ -3224,11 +3224,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>azconzabal juan manuel</t>
+          <t>astrada leonardo</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157">
@@ -3242,11 +3242,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>balbo abel</t>
+          <t>azconzabal juan manuel</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158">
@@ -3260,11 +3260,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>barbas juan</t>
+          <t>balbo abel</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159">
@@ -3278,11 +3278,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>bassedas christian</t>
+          <t>barbas juan</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="160">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>battaglia sebastian</t>
+          <t>bassedas christian</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161">
@@ -3314,11 +3314,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>bauza edgardo</t>
+          <t>battaglia sebastian</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162">
@@ -3332,11 +3332,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>beccacece sebastian</t>
+          <t>bauza edgardo</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="163">
@@ -3350,11 +3350,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>benitez leandro</t>
+          <t>beccacece sebastian</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="164">
@@ -3368,11 +3368,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>benitez leonardo</t>
+          <t>benitez leandro</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165">
@@ -3386,11 +3386,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>bernardi lucas</t>
+          <t>benitez leonardo</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166">
@@ -3404,11 +3404,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>beron fernando</t>
+          <t>bernardi lucas</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167">
@@ -3422,11 +3422,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>berti alfredo</t>
+          <t>beron fernando</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168">
@@ -3440,11 +3440,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>biaggio claudio</t>
+          <t>berti alfredo</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169">
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>bianchi carlos</t>
+          <t>biaggio claudio</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="170">
@@ -3476,11 +3476,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>bidoglio hector</t>
+          <t>bianchi carlos</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="171">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>borghi claudio</t>
+          <t>bidoglio hector</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="172">
@@ -3512,11 +3512,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>burgos german</t>
+          <t>borghi claudio</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="173">
@@ -3530,11 +3530,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>burruchaga jorge</t>
+          <t>burgos german</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="174">
@@ -3548,11 +3548,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>caixinha pedro</t>
+          <t>burruchaga jorge</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="175">
@@ -3566,11 +3566,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>camoranesi mauro</t>
+          <t>caixinha pedro</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176">
@@ -3584,11 +3584,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>carboni ezequiel</t>
+          <t>camoranesi mauro</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="177">
@@ -3602,11 +3602,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>caruso ricardo</t>
+          <t>carboni ezequiel</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178">
@@ -3620,11 +3620,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>castro fabian</t>
+          <t>caruso ricardo</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="179">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>cocca diego</t>
+          <t>castro fabian</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180">
@@ -3656,11 +3656,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>coleoni gustavo</t>
+          <t>cocca diego</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="181">
@@ -3674,11 +3674,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>comesana julio</t>
+          <t>coleoni gustavo</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="182">
@@ -3692,11 +3692,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>constantin julio</t>
+          <t>comesana julio</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="183">
@@ -3710,11 +3710,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>coria adrian</t>
+          <t>constantin julio</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184">
@@ -3728,11 +3728,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>coudet eduardo</t>
+          <t>coria adrian</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="185">
@@ -3746,11 +3746,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>coyette walter</t>
+          <t>coudet eduardo</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="186">
@@ -3764,11 +3764,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>crespo hernan</t>
+          <t>coyette walter</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="187">
@@ -3782,11 +3782,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>dabove diego</t>
+          <t>crespo hernan</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="188">
@@ -3800,11 +3800,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>damonte israel</t>
+          <t>dabove diego</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="189">
@@ -3818,11 +3818,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>de felippe omar</t>
+          <t>damonte israel</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="190">
@@ -3836,11 +3836,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>de muner pablo</t>
+          <t>de felippe omar</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="191">
@@ -3854,11 +3854,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>de paoli rodolfo</t>
+          <t>de muner pablo</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="192">
@@ -3872,11 +3872,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>delfino ivan</t>
+          <t>de paoli rodolfo</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="193">
@@ -3890,11 +3890,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>demichelis martin</t>
+          <t>delfino ivan</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="194">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>desabato leandro</t>
+          <t>demichelis martin</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="195">
@@ -3926,11 +3926,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>diaz cristian</t>
+          <t>desabato leandro</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="196">
@@ -3944,11 +3944,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>diaz ramon</t>
+          <t>diaz cristian</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="197">
@@ -3962,11 +3962,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>diez nicolas</t>
+          <t>diaz ramon</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="198">
@@ -3980,11 +3980,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>dominguez eduardo</t>
+          <t>diez nicolas</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="199">
@@ -3998,11 +3998,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>echeverria mariano</t>
+          <t>dominguez eduardo</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="200">
@@ -4016,11 +4016,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>erroz diego</t>
+          <t>echeverria mariano</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="201">
@@ -4034,11 +4034,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>esmerado gaston</t>
+          <t>erroz diego</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="202">
@@ -4052,11 +4052,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>espinola dario</t>
+          <t>esmerado gaston</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="203">
@@ -4070,11 +4070,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>falcioni julio</t>
+          <t>espinola dario</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="204">
@@ -4088,11 +4088,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>fernandez leonardo</t>
+          <t>falcioni julio</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="205">
@@ -4106,11 +4106,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>fernandez manuel</t>
+          <t>fernandez leonardo</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="206">
@@ -4124,11 +4124,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ferrari paulo</t>
+          <t>fernandez manuel</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="207">
@@ -4142,11 +4142,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ferrero alexis</t>
+          <t>ferrari paulo</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="208">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>fleitas juan ramon</t>
+          <t>ferrero alexis</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="209">
@@ -4178,11 +4178,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>flores diego</t>
+          <t>fleitas juan ramon</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="210">
@@ -4196,11 +4196,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>flores jose oscar</t>
+          <t>flores diego</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="211">
@@ -4214,11 +4214,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>forestello ruben dario</t>
+          <t>flores jose oscar</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="212">
@@ -4232,11 +4232,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>franco dario</t>
+          <t>forestello ruben dario</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="213">
@@ -4250,11 +4250,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>fuertes esteban</t>
+          <t>franco dario</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="214">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>funes martin</t>
+          <t>fuertes esteban</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="215">
@@ -4286,11 +4286,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>gago fernando</t>
+          <t>funes martin</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="216">
@@ -4304,11 +4304,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>gallardo marcelo</t>
+          <t>gago fernando</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="217">
@@ -4322,11 +4322,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>gallego americo</t>
+          <t>gallardo marcelo</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="218">
@@ -4340,11 +4340,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>galloni hugo</t>
+          <t>gallego americo</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="219">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>gamboa fernando</t>
+          <t>galloni hugo</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="220">
@@ -4376,11 +4376,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>gandolfi javier</t>
+          <t>gamboa fernando</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="221">
@@ -4394,11 +4394,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>gareca ricardo</t>
+          <t>gandolfi javier</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="222">
@@ -4412,11 +4412,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>garfagnoli fabian</t>
+          <t>gareca ricardo</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="223">
@@ -4430,11 +4430,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>giunta blas armando</t>
+          <t>garfagnoli fabian</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="224">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>gomez marcelo</t>
+          <t>giunta blas armando</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="225">
@@ -4466,11 +4466,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>gomez sergio</t>
+          <t>gomez marcelo</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="226">
@@ -4484,11 +4484,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>gonzalez esteban</t>
+          <t>gomez sergio</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="227">
@@ -4502,11 +4502,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>gonzalez kily</t>
+          <t>gonzalez esteban</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="228">
@@ -4520,11 +4520,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>gonzalez roberto</t>
+          <t>gonzalez kily</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="229">
@@ -4538,11 +4538,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>gorosito nestor</t>
+          <t>gonzalez roberto</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="230">
@@ -4556,11 +4556,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>goux marcelo</t>
+          <t>gorosito nestor</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="231">
@@ -4574,11 +4574,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>graciani gabriel</t>
+          <t>goux marcelo</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="232">
@@ -4592,11 +4592,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>graf claudio</t>
+          <t>graciani gabriel</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="233">
@@ -4610,11 +4610,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>grelak alfredo</t>
+          <t>graf claudio</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="234">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>grondona humberto</t>
+          <t>grelak alfredo</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="235">
@@ -4646,11 +4646,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>guede pablo</t>
+          <t>grondona humberto</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="236">
@@ -4664,11 +4664,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>guinazu pablo</t>
+          <t>guede pablo</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="237">
@@ -4682,11 +4682,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>gustavo tognarelli</t>
+          <t>guinazu pablo</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="238">
@@ -4700,11 +4700,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>heinze gabriel</t>
+          <t>gustavo tognarelli</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="239">
@@ -4718,11 +4718,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>herron mariano</t>
+          <t>heinze gabriel</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="240">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>holan ariel</t>
+          <t>herron mariano</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="241">
@@ -4754,11 +4754,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>hoyos angel guillermo</t>
+          <t>holan ariel</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="242">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ibarra hugo</t>
+          <t>hoyos angel guillermo</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="243">
@@ -4790,11 +4790,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>insua ruben</t>
+          <t>ibarra hugo</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="244">
@@ -4808,11 +4808,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>johansen ricardo</t>
+          <t>insua ruben</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="245">
@@ -4826,11 +4826,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>kudelka frank</t>
+          <t>johansen ricardo</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="246">
@@ -4844,11 +4844,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>larriera mauricio</t>
+          <t>kudelka frank</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="247">
@@ -4862,11 +4862,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>lavallen pablo</t>
+          <t>larriera mauricio</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="248">
@@ -4880,11 +4880,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ledesma cristian</t>
+          <t>lavallen pablo</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="249">
@@ -4898,11 +4898,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>lippi sergio</t>
+          <t>ledesma cristian</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="250">
@@ -4916,11 +4916,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>llop juan</t>
+          <t>lippi sergio</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="251">
@@ -4934,11 +4934,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>lunari ricardo</t>
+          <t>llop juan</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="252">
@@ -4952,11 +4952,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>madelon leonardo</t>
+          <t>lunari ricardo</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="253">
@@ -4970,11 +4970,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>maradona diego armando</t>
+          <t>madelon leonardo</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="254">
@@ -4988,11 +4988,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>marcelo saralegui</t>
+          <t>maradona diego armando</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="255">
@@ -5006,11 +5006,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>marini adrian</t>
+          <t>marcelo saralegui</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="256">
@@ -5024,11 +5024,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>marini pablo</t>
+          <t>marini adrian</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="257">
@@ -5042,11 +5042,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>martinez diego hernan</t>
+          <t>marini pablo</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="258">
@@ -5060,11 +5060,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>martini leandro</t>
+          <t>martinez diego hernan</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="259">
@@ -5078,11 +5078,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>matosas gustavo</t>
+          <t>martini leandro</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="260">
@@ -5096,11 +5096,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>mayor carlos</t>
+          <t>matosas gustavo</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="261">
@@ -5114,11 +5114,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>medina alexandre</t>
+          <t>mayor carlos</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="262">
@@ -5132,11 +5132,11 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>mendez sebastian</t>
+          <t>medina alexandre</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="263">
@@ -5150,11 +5150,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>merlo reinaldo carlos</t>
+          <t>mendez sebastian</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="264">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>messera mariano</t>
+          <t>merlo reinaldo carlos</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="265">
@@ -5186,11 +5186,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>milito gabriel</t>
+          <t>messera mariano</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="266">
@@ -5204,11 +5204,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>mohamed antonio</t>
+          <t>milito gabriel</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="267">
@@ -5222,11 +5222,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>monarriz diego</t>
+          <t>mohamed antonio</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="268">
@@ -5240,11 +5240,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>montero paolo</t>
+          <t>monarriz diego</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="269">
@@ -5258,11 +5258,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>mosset marcelo</t>
+          <t>montero paolo</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="270">
@@ -5276,11 +5276,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>munua gustavo</t>
+          <t>mosset marcelo</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="271">
@@ -5294,11 +5294,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>oldra daniel</t>
+          <t>munua gustavo</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="272">
@@ -5312,11 +5312,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>orsi favio</t>
+          <t>oldra daniel</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="273">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ortiz dario</t>
+          <t>orsi favio</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="274">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>osella diego</t>
+          <t>ortiz dario</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="275">
@@ -5366,11 +5366,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>palermo martin</t>
+          <t>osella diego</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="276">
@@ -5384,11 +5384,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>patalano alejandro</t>
+          <t>palermo martin</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="277">
@@ -5402,11 +5402,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>pellegrino mauricio</t>
+          <t>patalano alejandro</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="278">
@@ -5420,11 +5420,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>pena sebastian</t>
+          <t>pellegrino mauricio</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="279">
@@ -5438,11 +5438,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>perazzo walter</t>
+          <t>pena sebastian</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="280">
@@ -5456,11 +5456,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>pizzi juan</t>
+          <t>perazzo walter</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="281">
@@ -5474,11 +5474,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>precone luciano</t>
+          <t>pizzi juan</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="282">
@@ -5492,11 +5492,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>pumpido juan pablo</t>
+          <t>precone luciano</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="283">
@@ -5510,11 +5510,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>pusineri lucas</t>
+          <t>pumpido juan pablo</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="284">
@@ -5528,11 +5528,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>quattrocchi pablo</t>
+          <t>pusineri lucas</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="285">
@@ -5546,11 +5546,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>quiroz fernando</t>
+          <t>quattrocchi pablo</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="286">
@@ -5564,11 +5564,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>radaelli fabio</t>
+          <t>quiroz fernando</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="287">
@@ -5582,11 +5582,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>raggio gustavo daniel</t>
+          <t>radaelli fabio</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="288">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>rambert sebastian</t>
+          <t>raggio gustavo daniel</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="289">
@@ -5618,11 +5618,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>rezza ricardo</t>
+          <t>rambert sebastian</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="290">
@@ -5636,11 +5636,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>rivarola german</t>
+          <t>rezza ricardo</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="291">
@@ -5654,11 +5654,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>rodriguez ricardo jose</t>
+          <t>rivarola german</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="292">
@@ -5672,11 +5672,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>romagnoli leandro atilio</t>
+          <t>rodriguez ricardo jose</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="293">
@@ -5690,11 +5690,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>romero sebastian</t>
+          <t>romagnoli leandro atilio</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="294">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>rondina sergio</t>
+          <t>romero sebastian</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="295">
@@ -5726,11 +5726,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ruiz carlos</t>
+          <t>rondina sergio</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="296">
@@ -5744,11 +5744,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>russo miguel</t>
+          <t>ruiz carlos</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="297">
@@ -5762,11 +5762,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>sanguinetti javier</t>
+          <t>russo miguel</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="298">
@@ -5780,11 +5780,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>sanzotti raul</t>
+          <t>sanguinetti javier</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="299">
@@ -5798,11 +5798,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>sava facundo</t>
+          <t>sanzotti raul</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="300">
@@ -5816,11 +5816,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>schelotto guillermo</t>
+          <t>sava facundo</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="301">
@@ -5834,11 +5834,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>schurrer gabriel</t>
+          <t>schelotto guillermo</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="302">
@@ -5852,11 +5852,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>sciacqua mario</t>
+          <t>schurrer gabriel</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="303">
@@ -5870,11 +5870,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>sensini roberto</t>
+          <t>sciacqua mario</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="304">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>somoza leandro</t>
+          <t>sensini roberto</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="305">
@@ -5906,11 +5906,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>soso mariano</t>
+          <t>somoza leandro</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="306">
@@ -5924,11 +5924,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>sponton claudio</t>
+          <t>soso mariano</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="307">
@@ -5942,11 +5942,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>stillitano leandro</t>
+          <t>sponton claudio</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="308">
@@ -5960,11 +5960,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>taffarel adrian</t>
+          <t>stillitano leandro</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="309">
@@ -5978,11 +5978,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>tevez carlos</t>
+          <t>taffarel adrian</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="310">
@@ -5996,11 +5996,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>troglio pedro</t>
+          <t>tevez carlos</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="311">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>ubeda claudio</t>
+          <t>troglio pedro</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="312">
@@ -6032,11 +6032,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>vaccari julio</t>
+          <t>ubeda claudio</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="313">
@@ -6050,11 +6050,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>vella cristian</t>
+          <t>vaccari julio</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="314">
@@ -6068,11 +6068,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>villar diego</t>
+          <t>vella cristian</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="315">
@@ -6086,11 +6086,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>villar diego nicolas</t>
+          <t>villar diego</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="316">
@@ -6104,11 +6104,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>vivas claudio</t>
+          <t>villar diego nicolas</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="317">
@@ -6122,11 +6122,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>vivas nelson</t>
+          <t>vivas claudio</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="318">
@@ -6140,11 +6140,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>vojvoda juan pablo</t>
+          <t>vivas nelson</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="319">
@@ -6158,11 +6158,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>zielinski ricardo</t>
+          <t>vojvoda juan pablo</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="320">
@@ -6176,11 +6176,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>zubeldia luis</t>
+          <t>zielinski ricardo</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="321">
@@ -6189,16 +6189,16 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>dt_vis</t>
+          <t>dt_loc</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>acosta rodrigo</t>
+          <t>zubeldia luis</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
     </row>
     <row r="322">
@@ -6212,11 +6212,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>adrover adrian</t>
+          <t>acosta rodrigo</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -6230,11 +6230,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>aguirre diego</t>
+          <t>adrover adrian</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>alegre fabian</t>
+          <t>aguirre diego</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
@@ -6266,11 +6266,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>alfaro gustavo</t>
+          <t>alegre fabian</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326">
@@ -6284,11 +6284,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>almeyda matias</t>
+          <t>alfaro gustavo</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327">
@@ -6302,11 +6302,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>almiron jorge</t>
+          <t>almeyda matias</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="328">
@@ -6320,11 +6320,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>alvarez gustavo</t>
+          <t>almiron jorge</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329">
@@ -6338,11 +6338,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>anastacio martin</t>
+          <t>alvarez gustavo</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -6356,11 +6356,11 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>apuzzo nestor</t>
+          <t>anastacio martin</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="331">
@@ -6374,11 +6374,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>arruabarrena rodolfo</t>
+          <t>apuzzo nestor</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="332">
@@ -6392,11 +6392,11 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>astrada leonardo</t>
+          <t>arruabarrena rodolfo</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="333">
@@ -6410,11 +6410,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>azconzabal juan manuel</t>
+          <t>astrada leonardo</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="334">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>balbo abel</t>
+          <t>azconzabal juan manuel</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="335">
@@ -6446,11 +6446,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>barbas juan</t>
+          <t>balbo abel</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="336">
@@ -6464,11 +6464,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>bassedas christian</t>
+          <t>barbas juan</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="337">
@@ -6482,11 +6482,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>battaglia sebastian</t>
+          <t>bassedas christian</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="338">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>bauza edgardo</t>
+          <t>battaglia sebastian</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="339">
@@ -6518,11 +6518,11 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>beccacece sebastian</t>
+          <t>bauza edgardo</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="340">
@@ -6536,11 +6536,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>benitez leandro</t>
+          <t>beccacece sebastian</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="341">
@@ -6554,11 +6554,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>benitez leonardo</t>
+          <t>benitez leandro</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="342">
@@ -6572,11 +6572,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>bernardi lucas</t>
+          <t>benitez leonardo</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="343">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>beron fernando</t>
+          <t>bernardi lucas</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="344">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>berti alfredo</t>
+          <t>beron fernando</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="345">
@@ -6626,11 +6626,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>biaggio claudio</t>
+          <t>berti alfredo</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346">
@@ -6644,11 +6644,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>bianchi carlos</t>
+          <t>biaggio claudio</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="347">
@@ -6662,11 +6662,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>bidoglio hector</t>
+          <t>bianchi carlos</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="348">
@@ -6680,11 +6680,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>blengio juan</t>
+          <t>bidoglio hector</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="349">
@@ -6698,11 +6698,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>borghi claudio</t>
+          <t>blengio juan</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="350">
@@ -6716,11 +6716,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>bravo marcelo rene</t>
+          <t>borghi claudio</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351">
@@ -6734,11 +6734,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>burgos german</t>
+          <t>bravo marcelo rene</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="352">
@@ -6752,11 +6752,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>burruchaga jorge</t>
+          <t>burgos german</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="353">
@@ -6770,11 +6770,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>caixinha pedro</t>
+          <t>burruchaga jorge</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="354">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>camoranesi mauro</t>
+          <t>caixinha pedro</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="355">
@@ -6806,11 +6806,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>carboni ezequiel</t>
+          <t>camoranesi mauro</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="356">
@@ -6824,11 +6824,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>caruso ricardo</t>
+          <t>carboni ezequiel</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="357">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>castro fabian</t>
+          <t>caruso ricardo</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="358">
@@ -6860,11 +6860,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>cocca diego</t>
+          <t>castro fabian</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="359">
@@ -6878,11 +6878,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>coleoni gustavo</t>
+          <t>cocca diego</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="360">
@@ -6896,11 +6896,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>comesana julio</t>
+          <t>coleoni gustavo</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="361">
@@ -6914,11 +6914,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>coria adrian</t>
+          <t>comesana julio</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="362">
@@ -6932,11 +6932,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>coudet eduardo</t>
+          <t>coria adrian</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="363">
@@ -6950,11 +6950,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>coyette walter</t>
+          <t>coudet eduardo</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="364">
@@ -6968,11 +6968,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>crespo hernan</t>
+          <t>coyette walter</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="365">
@@ -6986,11 +6986,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>dabove diego</t>
+          <t>crespo hernan</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="366">
@@ -7004,11 +7004,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>damonte israel</t>
+          <t>dabove diego</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="367">
@@ -7022,11 +7022,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>de felippe omar</t>
+          <t>damonte israel</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="368">
@@ -7040,11 +7040,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>de leon martin</t>
+          <t>de felippe omar</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="369">
@@ -7058,11 +7058,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>de paoli rodolfo</t>
+          <t>de leon martin</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="370">
@@ -7076,11 +7076,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>delfino ivan</t>
+          <t>de paoli rodolfo</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="371">
@@ -7094,11 +7094,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>demichelis martin</t>
+          <t>delfino ivan</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="372">
@@ -7112,11 +7112,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>diaz cristian</t>
+          <t>demichelis martin</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="373">
@@ -7130,11 +7130,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>diaz ramon</t>
+          <t>diaz cristian</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="374">
@@ -7148,11 +7148,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>diez nicolas</t>
+          <t>diaz ramon</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="375">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>dominguez eduardo</t>
+          <t>diez nicolas</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="376">
@@ -7184,11 +7184,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>donato hugo</t>
+          <t>dominguez eduardo</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="377">
@@ -7202,11 +7202,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>echeverria mariano</t>
+          <t>donato hugo</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="378">
@@ -7220,11 +7220,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>erroz diego</t>
+          <t>echeverria mariano</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="379">
@@ -7238,11 +7238,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>esmerado gaston</t>
+          <t>erroz diego</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="380">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>espinola dario</t>
+          <t>esmerado gaston</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="381">
@@ -7274,11 +7274,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>falcioni julio</t>
+          <t>espinola dario</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="382">
@@ -7292,11 +7292,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>fernandez favio</t>
+          <t>falcioni julio</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="383">
@@ -7310,11 +7310,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>fernandez leonardo</t>
+          <t>fernandez favio</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="384">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>fernandez manuel</t>
+          <t>fernandez leonardo</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="385">
@@ -7346,11 +7346,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>ferrari paulo</t>
+          <t>fernandez manuel</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="386">
@@ -7364,11 +7364,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ferrero alexis</t>
+          <t>ferrari paulo</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="387">
@@ -7382,11 +7382,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>fleitas juan ramon</t>
+          <t>ferrero alexis</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="388">
@@ -7400,11 +7400,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>flores diego</t>
+          <t>fleitas juan ramon</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="389">
@@ -7418,11 +7418,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>flores jose oscar</t>
+          <t>flores diego</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="390">
@@ -7436,11 +7436,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>forestello ruben dario</t>
+          <t>flores jose oscar</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="391">
@@ -7454,11 +7454,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>franco dario</t>
+          <t>forestello ruben dario</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="392">
@@ -7472,11 +7472,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>fuertes esteban</t>
+          <t>franco dario</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="393">
@@ -7490,11 +7490,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>funes martin</t>
+          <t>fuertes esteban</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="394">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>gago fernando</t>
+          <t>funes martin</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="395">
@@ -7526,11 +7526,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>gallardo marcelo</t>
+          <t>gago fernando</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="396">
@@ -7544,11 +7544,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>gallego americo</t>
+          <t>gallardo marcelo</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="397">
@@ -7562,11 +7562,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>galloni hugo</t>
+          <t>gallego americo</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="398">
@@ -7580,11 +7580,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>gamboa fernando</t>
+          <t>galloni hugo</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="399">
@@ -7598,11 +7598,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>gandolfi javier</t>
+          <t>gamboa fernando</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="400">
@@ -7616,11 +7616,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>gareca ricardo</t>
+          <t>gandolfi javier</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="401">
@@ -7634,11 +7634,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>garfagnoli fabian</t>
+          <t>gareca ricardo</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="402">
@@ -7652,11 +7652,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>giunta blas armando</t>
+          <t>garfagnoli fabian</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="403">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>gomez marcelo</t>
+          <t>giunta blas armando</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="404">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>gomez sergio</t>
+          <t>gomez marcelo</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="405">
@@ -7706,11 +7706,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>gonzalez esteban</t>
+          <t>gomez sergio</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="406">
@@ -7724,11 +7724,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>gonzalez kily</t>
+          <t>gonzalez esteban</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="407">
@@ -7742,11 +7742,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>gonzalez roberto</t>
+          <t>gonzalez kily</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="408">
@@ -7760,11 +7760,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>gorosito nestor</t>
+          <t>gonzalez roberto</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="409">
@@ -7778,11 +7778,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>graf claudio</t>
+          <t>gorosito nestor</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="410">
@@ -7796,11 +7796,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>grelak alfredo</t>
+          <t>graf claudio</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="411">
@@ -7814,11 +7814,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>grondona humberto</t>
+          <t>grelak alfredo</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="412">
@@ -7832,11 +7832,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>guede pablo</t>
+          <t>grondona humberto</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="413">
@@ -7850,11 +7850,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>guinazu pablo</t>
+          <t>guede pablo</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="414">
@@ -7868,11 +7868,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>gustavo tognarelli</t>
+          <t>guinazu pablo</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="415">
@@ -7886,11 +7886,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>heinze gabriel</t>
+          <t>gustavo tognarelli</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="416">
@@ -7904,11 +7904,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>herron mariano</t>
+          <t>heinze gabriel</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="417">
@@ -7922,11 +7922,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>holan ariel</t>
+          <t>herron mariano</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="418">
@@ -7940,11 +7940,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>hoyos angel guillermo</t>
+          <t>holan ariel</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="419">
@@ -7958,11 +7958,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>ibarra hugo</t>
+          <t>hoyos angel guillermo</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="420">
@@ -7976,11 +7976,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>insua ruben</t>
+          <t>ibarra hugo</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="421">
@@ -7994,11 +7994,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>johansen ricardo</t>
+          <t>insua ruben</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="422">
@@ -8012,11 +8012,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>kudelka frank</t>
+          <t>johansen ricardo</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="423">
@@ -8030,11 +8030,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>larriera mauricio</t>
+          <t>kudelka frank</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="424">
@@ -8048,11 +8048,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>lavallen pablo</t>
+          <t>larriera mauricio</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="425">
@@ -8066,11 +8066,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>ledesma cristian</t>
+          <t>lavallen pablo</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="426">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>lippi sergio</t>
+          <t>ledesma cristian</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="427">
@@ -8102,11 +8102,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>llop juan</t>
+          <t>lippi sergio</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="428">
@@ -8120,11 +8120,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>lunari ricardo</t>
+          <t>llop juan</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="429">
@@ -8138,11 +8138,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>madelon leonardo</t>
+          <t>lunari ricardo</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="430">
@@ -8156,11 +8156,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>maradona diego armando</t>
+          <t>madelon leonardo</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="431">
@@ -8174,11 +8174,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>marcelo saralegui</t>
+          <t>maradona diego armando</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="432">
@@ -8192,11 +8192,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>marini adrian</t>
+          <t>marcelo saralegui</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="433">
@@ -8210,11 +8210,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>marini pablo</t>
+          <t>marini adrian</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="434">
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>markic diego</t>
+          <t>marini pablo</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="435">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>martinez diego hernan</t>
+          <t>markic diego</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="436">
@@ -8264,11 +8264,11 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>martini leandro</t>
+          <t>martinez diego hernan</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="437">
@@ -8282,11 +8282,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>matosas gustavo</t>
+          <t>martini leandro</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="438">
@@ -8300,11 +8300,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>mayor carlos</t>
+          <t>matosas gustavo</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="439">
@@ -8318,11 +8318,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>medina alexandre</t>
+          <t>mayor carlos</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="440">
@@ -8336,11 +8336,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>mendez sebastian</t>
+          <t>medina alexandre</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="441">
@@ -8354,11 +8354,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>merlo reinaldo carlos</t>
+          <t>mendez sebastian</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="442">
@@ -8372,11 +8372,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>messera mariano</t>
+          <t>merlo reinaldo carlos</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="443">
@@ -8390,11 +8390,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>milito gabriel</t>
+          <t>messera mariano</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="444">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>mohamed antonio</t>
+          <t>milito gabriel</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="445">
@@ -8426,11 +8426,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>monarriz diego</t>
+          <t>mohamed antonio</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="446">
@@ -8444,11 +8444,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>montero paolo</t>
+          <t>monarriz diego</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="447">
@@ -8462,11 +8462,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>mosset marcelo</t>
+          <t>montero paolo</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="448">
@@ -8480,11 +8480,11 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>munua gustavo</t>
+          <t>mosset marcelo</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="449">
@@ -8498,11 +8498,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>oldra daniel</t>
+          <t>munua gustavo</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="450">
@@ -8516,11 +8516,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>orsi favio</t>
+          <t>oldra daniel</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="451">
@@ -8534,11 +8534,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>ortiz dario</t>
+          <t>orsi favio</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="452">
@@ -8552,11 +8552,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>osella diego</t>
+          <t>ortiz dario</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="453">
@@ -8570,11 +8570,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>palermo martin</t>
+          <t>osella diego</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="454">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>patalano alejandro</t>
+          <t>otta walter</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="455">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>pellegrino mauricio</t>
+          <t>palermo martin</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="456">
@@ -8624,11 +8624,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>pena sebastian</t>
+          <t>patalano alejandro</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="457">
@@ -8642,11 +8642,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>perazzo walter</t>
+          <t>pellegrino mauricio</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="458">
@@ -8660,11 +8660,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>picerni carlos</t>
+          <t>pena sebastian</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="459">
@@ -8678,11 +8678,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>pizzi juan</t>
+          <t>perazzo walter</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="460">
@@ -8696,11 +8696,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>precone luciano</t>
+          <t>picerni carlos</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="461">
@@ -8714,11 +8714,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>pumpido juan pablo</t>
+          <t>pizzi juan</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="462">
@@ -8732,11 +8732,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>pusineri lucas</t>
+          <t>precone luciano</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="463">
@@ -8750,11 +8750,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>quattrocchi pablo</t>
+          <t>pumpido juan pablo</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="464">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>quiroz fernando</t>
+          <t>pusineri lucas</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="465">
@@ -8786,11 +8786,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>radaelli fabio</t>
+          <t>quattrocchi pablo</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="466">
@@ -8804,11 +8804,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>raggio gustavo daniel</t>
+          <t>quiroz fernando</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="467">
@@ -8822,11 +8822,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>rambert sebastian</t>
+          <t>radaelli fabio</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="468">
@@ -8840,11 +8840,11 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>rezza ricardo</t>
+          <t>raggio gustavo daniel</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="469">
@@ -8858,11 +8858,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>rivarola german</t>
+          <t>rambert sebastian</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="470">
@@ -8876,11 +8876,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>rodriguez ricardo jose</t>
+          <t>rezza ricardo</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="471">
@@ -8894,11 +8894,11 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>romagnoli leandro atilio</t>
+          <t>rivarola german</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="472">
@@ -8912,11 +8912,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>romero sebastian</t>
+          <t>rodriguez ricardo jose</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="473">
@@ -8930,11 +8930,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>rondina sergio</t>
+          <t>romagnoli leandro atilio</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="474">
@@ -8948,11 +8948,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>ruiz carlos</t>
+          <t>romero sebastian</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="475">
@@ -8966,11 +8966,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>russo miguel</t>
+          <t>rondina sergio</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="476">
@@ -8984,11 +8984,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>sanguinetti guillermo</t>
+          <t>ruiz carlos</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="477">
@@ -9002,11 +9002,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>sanguinetti javier</t>
+          <t>russo miguel</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="478">
@@ -9020,11 +9020,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>sanzotti raul</t>
+          <t>sanguinetti guillermo</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="479">
@@ -9038,11 +9038,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>sava facundo</t>
+          <t>sanguinetti javier</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="480">
@@ -9056,11 +9056,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>schelotto guillermo</t>
+          <t>sanzotti raul</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="481">
@@ -9074,11 +9074,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>schurrer gabriel</t>
+          <t>sava facundo</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="482">
@@ -9092,11 +9092,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>sciacqua mario</t>
+          <t>schelotto guillermo</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="483">
@@ -9110,11 +9110,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>scolari sebastian</t>
+          <t>schurrer gabriel</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="484">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>sensini roberto</t>
+          <t>sciacqua mario</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="485">
@@ -9146,11 +9146,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>serrizuela juan jose</t>
+          <t>scolari sebastian</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="486">
@@ -9164,11 +9164,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>somoza leandro</t>
+          <t>sensini roberto</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="487">
@@ -9182,11 +9182,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>soso mariano</t>
+          <t>serrizuela juan jose</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="488">
@@ -9200,11 +9200,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>sponton claudio</t>
+          <t>somoza leandro</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="489">
@@ -9218,11 +9218,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>stillitano leandro</t>
+          <t>soso mariano</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="490">
@@ -9236,11 +9236,11 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>taffarel adrian</t>
+          <t>sponton claudio</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="491">
@@ -9254,11 +9254,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>tevez carlos</t>
+          <t>stillitano leandro</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="492">
@@ -9272,11 +9272,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>tocalli hugo</t>
+          <t>taffarel adrian</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="493">
@@ -9290,11 +9290,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>troglio pedro</t>
+          <t>tevez carlos</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="494">
@@ -9308,11 +9308,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>ubeda claudio</t>
+          <t>tocalli hugo</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="495">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>vaccari julio</t>
+          <t>troglio pedro</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="496">
@@ -9344,11 +9344,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>vella cristian</t>
+          <t>ubeda claudio</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="497">
@@ -9362,11 +9362,11 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>villar diego</t>
+          <t>vaccari julio</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="498">
@@ -9380,11 +9380,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>villar diego nicolas</t>
+          <t>vella cristian</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="499">
@@ -9398,11 +9398,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>vivas claudio</t>
+          <t>villar diego</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="500">
@@ -9416,11 +9416,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>vivas nelson</t>
+          <t>villar diego nicolas</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="501">
@@ -9434,11 +9434,11 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>vojvoda juan pablo</t>
+          <t>vivas claudio</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="502">
@@ -9452,11 +9452,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>zielinski ricardo</t>
+          <t>vivas nelson</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="503">
@@ -9470,11 +9470,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>zubeldia luis</t>
+          <t>vojvoda juan pablo</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="504">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>equipo_ganador</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Empate</t>
+          <t>zielinski ricardo</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
     </row>
     <row r="505">
@@ -9501,16 +9501,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>equipo_ganador</t>
+          <t>dt_vis</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>zubeldia luis</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
     </row>
     <row r="506">
@@ -9524,10 +9524,46 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>505</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>equipo_ganador</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>506</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>equipo_ganador</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
           <t>Visitante</t>
         </is>
       </c>
-      <c r="D506" t="n">
+      <c r="D508" t="n">
         <v>2</v>
       </c>
     </row>
